--- a/Paket_3_Bahasa_Indonesia_TKA_SD.xlsx
+++ b/Paket_3_Bahasa_Indonesia_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 3 Bahasa" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 1: contoh soal pemahaman teks.</t>
+          <t>Berdasarkan teks bacaan, apa fungsi utama dari organisasi tradisional Subak di Bali?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Menentukan harga jual gabah di pasar tradisional Bali</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Mengatur sistem pengairan persawahan secara adil dan demokratis</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Membuat pupuk organik dari tanaman kawah pegunungan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Membangun penginapan wisata di area perbukitan terasering</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 2: contoh soal pemahaman teks.</t>
+          <t>Filosofi 'Tri Hita Karana' yang melandasi sistem subak mengajarkan tentang....</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Persaingan hasil panen antarpetani di pulau Bali</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Tiga jenis tanaman wajib yang harus ditanam di sawah bertingkat</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Keselarasan hubungan manusia dengan Tuhan, sesama manusia, dan alam lingkungan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Tata cara membangun bendungan air tanpa menggunakan semen</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 3: contoh soal pemahaman teks.</t>
+          <t>Makna istilah 'terasering' pada paragraf pertama teks tersebut adalah....</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Sistem penanaman padi tanpa menggunakan lumpur</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Bangunan saluran air bawah tanah terpanjang di Asia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Teknik penataan lahan pertanian miring yang dibuat berundak-undak untuk mencegah erosi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Alat pengukur debit air yang terbuat dari bambu runcing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,37 +592,41 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 4: contoh soal pemahaman teks.</t>
+          <t>Manakah pernyataan berikut yang SESUAI dengan isi teks mengenai sistem Subak? (Pilihlah lebih dari satu jawaban benar!)  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Sistem subak telah diterapkan oleh petani Bali sejak abad ke-11.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Subak diakui oleh UNESCO sebagai Warisan Budaya Dunia pada tahun 2012.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Para petani Bali sering bersengketa memperebutkan air di musim kemarau.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Air irigasi subak dialirkan melalui saluran terowongan dan parit terasering.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,7 +637,11 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,27 +651,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 5: contoh soal pemahaman teks.</t>
+          <t>Ide pokok yang terdapat pada paragraf kedua teks informasi di atas adalah....</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Teknik penggalian terowongan bawah tanah di Bali</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Tahun peresmian UNESCO untuk kawasan wisata pegunungan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Filosofi Tri Hita Karana dan pengakuan dunia terhadap sistem subak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kekeringan yang melanda petak sawah para petani saat musim kemarau</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,17 +682,21 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 6: contoh soal pemahaman teks.</t>
+          <t>Tentukan kebenaran dari setiap pernyataan berikut berdasarkan teks bacaan subak!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -707,7 +727,11 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,27 +741,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 7: contoh soal pemahaman teks.</t>
+          <t>Simpulan yang paling tepat dari teks bacaan mengenai Subak adalah.... Bacalah cerita fiksi berikut dengan cermat untuk menjawab soal nomor 8 sampai 14!
+Semut Merah dan Sebutir Jagung Manis
+Di bawah rindangnya pohon mangga di pekarangan rumah, sekelompok semut merah sedang sibuk mencari persediaan makanan sebelum musim penghujan tiba. Samin, seekor semut muda yang gesit, menemukan sebutir biji jagung manis kering yang tergeletak di sela bebatuan. Biji jagung itu sangat besar dan berat, ukurannya hampir sepuluh kali lipat tubuh Samin.
+Samin berusaha sekuat tenaga mendorong biji jagung tersebut seorang diri. Namun, setelah berulang kali mencoba hingga napasnya tersengal-sengal, biji jagung itu hanya bergeser beberapa milimeter. Merasa tenaganya terkuras, Samin sempat merasa putus asa.
+Tiba-tiba, Dito, tetua semut yang melintas, menepuk pundak Samin sambil tersenyum hangat. "Samin, beban yang teramat berat tidak diciptakan untuk dipikul oleh sepasang pundak saja. Panggillah kawan-kawanmu." Samin segera menyadari kekeliruannya. Ia meniup peluit dari rumput untuk mengumpulkan kawan-kawannya. Puluhan semut merah pun datang berbondong-bondong. Mereka saling bahu-membahu dan bergotong royong mengangkat biji jagung manis tersebut. Dalam hitungan menit, biji jagung berhasil dibawa masuk ke dalam sarang dengan sorak gembira.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Sistem pertanian modern harus menghapus tradisi lama agar hasil panen melimpah.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Subak merupakan warisan budaya luhur yang memadukan kearifan lokal, pembagian air adil, dan pelestarian alam.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Semua sawah di Indonesia harus diubah menjadi terasering bertingkat seperti di Bali.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  UNESCO hanya memberikan penghargaan kepada sistem pengairan yang memakai terowongan.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -748,7 +776,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +790,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 8: contoh soal pemahaman teks.</t>
+          <t>Bagaimana sifat tokoh Samin pada awal cerita sebelum dinasihati oleh Tetua Dito?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Pemalas dan suka menyuruh kawan-kawannya</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Gigih namun memaksakan diri bekerja sendirian dan sempat putus asa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Kikir dan ingin memakan biji jagung seorang diri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Pengecut dan takut keluar dari sarang pohon mangga</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +821,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +835,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 9: contoh soal pemahaman teks.</t>
+          <t>Makna ungkapan 'bahu-membahu' pada paragraf terakhir cerita di atas adalah....</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Saling mengadu kekuatan fisik</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Bekerja sama dan tolong-menolong menyelesaikan pekerjaan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Berjalan berbaris beriringan secara rapi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Bersandar pada pundak kawan karena kelelahan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +866,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +880,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 10: contoh soal pemahaman teks.</t>
+          <t>Bagaimana cara para semut merah akhirnya berhasil membawa biji jagung manis yang berat ke dalam sarang?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Menunggu biji jagung tersebut hancur terkena air hujan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Meminta bantuan burung merpati untuk menerbangkannya</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Bergotong royong mengangkat biji jagung bersama puluhan semut lainnya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Memotong-motong biji jagung menjadi serpihan kecil seorang diri</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,37 +911,41 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 11: contoh soal pemahaman teks.</t>
+          <t>Nasihat apa yang disampaikan Tetua Dito kepada Samin ketika melihatnya kelelahan?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Beban yang teramat berat tidak diciptakan untuk dipikul sendirian.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Tinggalkan biji jagung itu karena mencari makanan lain jauh lebih mudah.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Mintalah bantuan kawan-kawanmu agar pekerjaan menjadi ringan.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Teruslah mendorong biji jagung sampai esok pagi.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,7 +956,11 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,27 +970,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 12: contoh soal pemahaman teks.</t>
+          <t>Amanat utama yang ingin disampaikan oleh pengarang melalui cerita semut tersebut adalah....</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Jangan pernah mencari makanan saat musim hujan tiba</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Berat sama dipikul, ringan sama dijinjing melalui semangat gotong royong</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Simpanlah makanan sebanyak-banyaknya untuk diri sendiri</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Biji jagung adalah makanan terbaik bagi hewan kecil</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,17 +1001,21 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 13: contoh soal pemahaman teks.</t>
+          <t>Tentukan kesesuaian dari pernyataan berikut terkait pesan moral cerita semut merah!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -994,7 +1046,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1060,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 14: contoh soal pemahaman teks.</t>
+          <t>Peribahasa yang paling tepat untuk menggambarkan keberhasilan kerja sama para semut merah adalah....</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Air beriak tanda tak dalam</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Bersatu kita teguh, bercerai kita runtuh</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Tong kosong nyaring bunyinya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Ada udang di balik batu</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,7 +1091,11 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1045,27 +1105,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 15: contoh soal pemahaman teks.</t>
+          <t>Penulisan huruf kapital yang tepat pada penulisan nama orang dan gelar kehormatan adalah....</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Seminar literasi anak tersebut dihadiri oleh dokter Raden Mas Danang, M.Pd.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Seminar literasi anak tersebut dihadiri oleh Dokter raden mas Danang, m.pd.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Seminar literasi anak tersebut dihadiri oleh dr. Raden Mas Danang, M.Pd.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Seminar literasi anak tersebut dihadiri oleh Dr. raden Mas Danang, M.pd.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1076,7 +1136,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1150,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 16: contoh soal pemahaman teks.</t>
+          <t>Penggunaan tanda petik yang tepat terdapat pada kalimat....</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Siswa kelas 6 sedang menyanyikan lagu "Tanah Airku" di aula sekolah.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Siswa kelas 6 sedang menyanyikan lagu 'Tanah Airku' di aula sekolah.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Siswa kelas 6 sedang menyanyikan lagu: "Tanah Airku" di aula sekolah.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Siswa kelas 6 sedang menyanyikan lagu (Tanah Airku) di aula sekolah.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1181,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1195,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 17: contoh soal pemahaman teks.</t>
+          <t>Pilihlah deretan kata yang SEMUANYA merupakan kata baku menurut KBBI!</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Antre, cabai, objek, risiko</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Antri, cabe, obyek, resiko</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Antre, cabe, objek, resiko</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Antri, cabai, obyek, risiko</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,37 +1226,43 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 18: contoh soal pemahaman teks.</t>
+          <t>Perhatikan kalimat berikut:
+"Pagi hari cuaca di desa tampak cerah berawan. [...], menjelang siang hujan deras mengguyur pekarangan rumah."
+Kata penghubung antarkalimat yang TEPAT untuk melengkapi kalimat tersebut adalah....  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Namun</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Akan tetapi</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Karena itu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Sehingga</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1273,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1287,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 19: contoh soal pemahaman teks.</t>
+          <t>Perhatikan langkah-langkah membuat pupuk kompos sederhana berikut:
+(1) Siram tumpukan sampah organik dengan air secukupnya agar lembap.
+(2) Kumpulkan sisa sayuran dan daun kering ke dalam wadah pengomposan.
+(3) Diamkan dan aduk campuran kompos seminggu sekali selama 1 bulan.
+(4) Tutup wadah dengan rapat dan letakkan di tempat yang teduh.
+Urutan pembuatan kompos yang tepat adalah....</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  (2) - (1) - (4) - (3)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  (2) - (4) - (1) - (3)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  (1) - (2) - (3) - (4)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  (2) - (3) - (1) - (4)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1323,21 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 3] Soal Bahasa 20: contoh soal pemahaman teks.</t>
+          <t>Tentukan kebenaran dari penilaian efektivitas kalimat berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1368,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
